--- a/data/processed/harmonization/Nitrogen__Total_nitrogen/10.25581_ornlsfa.024_1837084/10.25581_ornlsfa.024_1837084_soil_Nitrogen__Total_nitrogen.xlsx
+++ b/data/processed/harmonization/Nitrogen__Total_nitrogen/10.25581_ornlsfa.024_1837084/10.25581_ornlsfa.024_1837084_soil_Nitrogen__Total_nitrogen.xlsx
@@ -426,13 +426,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M109"/>
+  <dimension ref="A1:L109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
@@ -440,8 +440,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -502,11 +501,6 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>source_row</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
           <t>notes</t>
         </is>
       </c>
@@ -524,12 +518,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A17.5</t>
+          <t>2019-03-SC-A17.5:1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -557,12 +551,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -579,12 +570,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A17.5</t>
+          <t>2019-03-SC-A17.5:2</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -612,12 +603,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -634,12 +622,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B17.5</t>
+          <t>2019-03-SC-B17.5:1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -667,12 +655,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -689,12 +674,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B17.5</t>
+          <t>2019-03-SC-B17.5:2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -722,12 +707,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -744,12 +726,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C17.5</t>
+          <t>2019-03-SC-C17.5:1</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -777,12 +759,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -799,12 +778,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C17.5</t>
+          <t>2019-03-SC-C17.5:2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -832,12 +811,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -854,12 +830,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A27.5</t>
+          <t>2019-03-SC-A27.5:1</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -887,12 +863,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -909,12 +882,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A27.5</t>
+          <t>2019-03-SC-A27.5:2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -942,12 +915,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -964,12 +934,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B27.5</t>
+          <t>2019-03-SC-B27.5:1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -997,12 +967,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -1019,12 +986,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B27.5</t>
+          <t>2019-03-SC-B27.5:2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1052,12 +1019,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1038,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C27.5</t>
+          <t>2019-03-SC-C27.5:1</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1107,12 +1071,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1090,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C27.5</t>
+          <t>2019-03-SC-C27.5:2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1162,12 +1123,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1142,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A37.5</t>
+          <t>2019-03-SC-A37.5:1</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1217,12 +1175,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1194,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A37.5</t>
+          <t>2019-03-SC-A37.5:2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1272,12 +1227,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1246,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B37.5</t>
+          <t>2019-03-SC-B37.5:1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1327,12 +1279,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1298,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B37.5</t>
+          <t>2019-03-SC-B37.5:2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1382,12 +1331,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -1404,12 +1350,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C37.5</t>
+          <t>2019-03-SC-C37.5:1</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1437,12 +1383,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -1459,12 +1402,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C37.5</t>
+          <t>2019-03-SC-C37.5:2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1492,12 +1435,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -1514,12 +1454,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A47.5</t>
+          <t>2019-03-SC-A47.5:1</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1547,12 +1487,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -1569,12 +1506,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A47.5</t>
+          <t>2019-03-SC-A47.5:2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1602,12 +1539,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1558,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B47.5</t>
+          <t>2019-03-SC-B47.5:1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1657,12 +1591,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1610,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B47.5</t>
+          <t>2019-03-SC-B47.5:2</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1712,12 +1643,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -1734,12 +1662,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C47.5</t>
+          <t>2019-03-SC-C47.5:1</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1767,12 +1695,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1714,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C47.5</t>
+          <t>2019-03-SC-C47.5:2</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1822,12 +1747,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1766,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A57.5</t>
+          <t>2019-03-SC-A57.5:1</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1877,12 +1799,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -1899,12 +1818,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A57.5</t>
+          <t>2019-03-SC-A57.5:2</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1932,12 +1851,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -1954,12 +1870,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B57.5</t>
+          <t>2019-03-SC-B57.5:1</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1987,12 +1903,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -2009,12 +1922,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B57.5</t>
+          <t>2019-03-SC-B57.5:2</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2042,12 +1955,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -2064,12 +1974,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C57.5</t>
+          <t>2019-03-SC-C57.5:1</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2097,12 +2007,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -2119,12 +2026,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C57.5</t>
+          <t>2019-03-SC-C57.5:2</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2152,12 +2059,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -2174,12 +2078,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A67.5</t>
+          <t>2019-03-SC-A67.5:1</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2207,12 +2111,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -2229,12 +2130,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A67.5</t>
+          <t>2019-03-SC-A67.5:2</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2262,12 +2163,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -2284,12 +2182,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B67.5</t>
+          <t>2019-03-SC-B67.5:1</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2317,12 +2215,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -2339,12 +2234,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B67.5</t>
+          <t>2019-03-SC-B67.5:2</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2372,12 +2267,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -2394,12 +2286,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C67.5</t>
+          <t>2019-03-SC-C67.5:1</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2427,12 +2319,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2338,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C67.5</t>
+          <t>2019-03-SC-C67.5:2</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2482,12 +2371,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -2504,12 +2390,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A115</t>
+          <t>2019-03-SC-A115:1</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2537,12 +2423,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2442,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A115</t>
+          <t>2019-03-SC-A115:2</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2592,12 +2475,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -2614,12 +2494,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B115</t>
+          <t>2019-03-SC-B115:1</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2647,12 +2527,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2546,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B115</t>
+          <t>2019-03-SC-B115:2</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2702,12 +2579,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -2724,12 +2598,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C115</t>
+          <t>2019-03-SC-C115:1</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2757,12 +2631,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2650,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C115</t>
+          <t>2019-03-SC-C115:2</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2812,12 +2683,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -2834,12 +2702,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A215</t>
+          <t>2019-03-SC-A215:1</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2867,12 +2735,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2754,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A215</t>
+          <t>2019-03-SC-A215:2</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2922,12 +2787,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -2944,12 +2806,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B215</t>
+          <t>2019-03-SC-B215:1</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2977,12 +2839,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -2999,12 +2858,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B215</t>
+          <t>2019-03-SC-B215:2</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -3032,12 +2891,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -3054,12 +2910,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C215</t>
+          <t>2019-03-SC-C215:1</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -3087,12 +2943,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -3109,12 +2962,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C215</t>
+          <t>2019-03-SC-C215:2</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -3142,12 +2995,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -3164,12 +3014,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A315</t>
+          <t>2019-03-SC-A315:1</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -3197,12 +3047,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -3219,12 +3066,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A315</t>
+          <t>2019-03-SC-A315:2</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3252,12 +3099,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -3274,12 +3118,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B315</t>
+          <t>2019-03-SC-B315:1</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3307,12 +3151,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -3329,12 +3170,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B315</t>
+          <t>2019-03-SC-B315:2</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3362,12 +3203,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -3384,12 +3222,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C315</t>
+          <t>2019-03-SC-C315:1</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3417,12 +3255,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -3439,12 +3274,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C315</t>
+          <t>2019-03-SC-C315:2</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3472,12 +3307,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -3494,12 +3326,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A415</t>
+          <t>2019-03-SC-A415:1</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3527,12 +3359,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -3549,12 +3378,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A415</t>
+          <t>2019-03-SC-A415:2</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3582,12 +3411,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -3604,12 +3430,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B415</t>
+          <t>2019-03-SC-B415:1</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3637,12 +3463,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -3659,12 +3482,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B415</t>
+          <t>2019-03-SC-B415:2</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3692,12 +3515,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -3714,12 +3534,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C415</t>
+          <t>2019-03-SC-C415:1</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3747,12 +3567,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -3769,12 +3586,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C415</t>
+          <t>2019-03-SC-C415:2</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3802,12 +3619,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
-      <c r="L61" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3638,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A515</t>
+          <t>2019-03-SC-A515:1</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3857,12 +3671,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -3879,12 +3690,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A515</t>
+          <t>2019-03-SC-A515:2</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3912,12 +3723,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -3934,12 +3742,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B515</t>
+          <t>2019-03-SC-B515:1</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3967,12 +3775,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="2" t="n">
-        <v>94</v>
-      </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -3989,12 +3794,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B515</t>
+          <t>2019-03-SC-B515:2</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -4022,12 +3827,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
-      <c r="L65" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -4044,12 +3846,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C515</t>
+          <t>2019-03-SC-C515:1</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -4077,12 +3879,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K66" s="2" t="inlineStr"/>
-      <c r="L66" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -4099,12 +3898,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C515</t>
+          <t>2019-03-SC-C515:2</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -4132,12 +3931,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
-      <c r="L67" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -4154,12 +3950,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A615</t>
+          <t>2019-03-SC-A615:1</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -4187,12 +3983,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
-      <c r="L68" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -4209,12 +4002,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A615</t>
+          <t>2019-03-SC-A615:2</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -4242,12 +4035,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
-      <c r="L69" s="2" t="n">
-        <v>101</v>
-      </c>
-      <c r="M69" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -4264,12 +4054,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B615</t>
+          <t>2019-03-SC-B615:1</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -4297,12 +4087,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="n">
-        <v>103</v>
-      </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -4319,12 +4106,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B615</t>
+          <t>2019-03-SC-B615:2</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -4352,12 +4139,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="2" t="n">
-        <v>104</v>
-      </c>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4158,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C615</t>
+          <t>2019-03-SC-C615:1</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -4407,12 +4191,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="2" t="n">
-        <v>106</v>
-      </c>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -4429,12 +4210,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C615</t>
+          <t>2019-03-SC-C615:2</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -4462,12 +4243,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -4484,12 +4262,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A130</t>
+          <t>2019-03-SC-A130:1</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -4517,12 +4295,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="M74" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -4539,12 +4314,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A130</t>
+          <t>2019-03-SC-A130:2</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -4572,12 +4347,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
-      <c r="L75" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4366,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B130</t>
+          <t>2019-03-SC-B130:1</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4627,12 +4399,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="n">
-        <v>112</v>
-      </c>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -4649,12 +4418,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B130</t>
+          <t>2019-03-SC-B130:2</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4682,12 +4451,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
-      <c r="L77" s="2" t="n">
-        <v>113</v>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -4704,12 +4470,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C130</t>
+          <t>2019-03-SC-C130:1</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4737,12 +4503,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -4759,12 +4522,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C130</t>
+          <t>2019-03-SC-C130:2</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4792,12 +4555,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="2" t="n">
-        <v>116</v>
-      </c>
-      <c r="M79" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -4814,12 +4574,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A230</t>
+          <t>2019-03-SC-A230:1</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4847,12 +4607,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="n">
-        <v>118</v>
-      </c>
-      <c r="M80" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -4869,12 +4626,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A230</t>
+          <t>2019-03-SC-A230:2</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -4902,12 +4659,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
-      <c r="L81" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="M81" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -4924,12 +4678,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B230</t>
+          <t>2019-03-SC-B230:1</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4957,12 +4711,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="2" t="n">
-        <v>121</v>
-      </c>
-      <c r="M82" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -4979,12 +4730,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B230</t>
+          <t>2019-03-SC-B230:2</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -5012,12 +4763,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K83" s="2" t="inlineStr"/>
-      <c r="L83" s="2" t="n">
-        <v>122</v>
-      </c>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -5034,12 +4782,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C230</t>
+          <t>2019-03-SC-C230:1</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -5067,12 +4815,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K84" s="2" t="inlineStr"/>
-      <c r="L84" s="2" t="n">
-        <v>124</v>
-      </c>
-      <c r="M84" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -5089,12 +4834,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C230</t>
+          <t>2019-03-SC-C230:2</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -5122,12 +4867,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K85" s="2" t="inlineStr"/>
-      <c r="L85" s="2" t="n">
-        <v>125</v>
-      </c>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -5144,12 +4886,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A330</t>
+          <t>2019-03-SC-A330:1</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -5177,12 +4919,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K86" s="2" t="inlineStr"/>
-      <c r="L86" s="2" t="n">
-        <v>127</v>
-      </c>
-      <c r="M86" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -5199,12 +4938,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A330</t>
+          <t>2019-03-SC-A330:2</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -5232,12 +4971,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K87" s="2" t="inlineStr"/>
-      <c r="L87" s="2" t="n">
-        <v>128</v>
-      </c>
-      <c r="M87" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -5254,12 +4990,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B330</t>
+          <t>2019-03-SC-B330:1</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -5287,12 +5023,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="2" t="n">
-        <v>130</v>
-      </c>
-      <c r="M88" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -5309,12 +5042,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B330</t>
+          <t>2019-03-SC-B330:2</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -5342,12 +5075,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K89" s="2" t="inlineStr"/>
-      <c r="L89" s="2" t="n">
-        <v>131</v>
-      </c>
-      <c r="M89" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -5364,12 +5094,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C330</t>
+          <t>2019-03-SC-C330:1</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -5397,12 +5127,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K90" s="2" t="inlineStr"/>
-      <c r="L90" s="2" t="n">
-        <v>133</v>
-      </c>
-      <c r="M90" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -5419,12 +5146,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C330</t>
+          <t>2019-03-SC-C330:2</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -5452,12 +5179,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
-      <c r="L91" s="2" t="n">
-        <v>134</v>
-      </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -5474,12 +5198,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A430</t>
+          <t>2019-03-SC-A430:1</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -5507,12 +5231,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
-      <c r="L92" s="2" t="n">
-        <v>136</v>
-      </c>
-      <c r="M92" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5250,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A430</t>
+          <t>2019-03-SC-A430:2</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -5562,12 +5283,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
-      <c r="L93" s="2" t="n">
-        <v>137</v>
-      </c>
-      <c r="M93" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -5584,12 +5302,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B430</t>
+          <t>2019-03-SC-B430:1</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -5617,12 +5335,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
-      <c r="L94" s="2" t="n">
-        <v>139</v>
-      </c>
-      <c r="M94" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5354,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B430</t>
+          <t>2019-03-SC-B430:2</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -5672,12 +5387,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
-      <c r="L95" s="2" t="n">
-        <v>140</v>
-      </c>
-      <c r="M95" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -5694,12 +5406,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C430</t>
+          <t>2019-03-SC-C430:1</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -5727,12 +5439,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
-      <c r="L96" s="2" t="n">
-        <v>142</v>
-      </c>
-      <c r="M96" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -5749,12 +5458,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C430</t>
+          <t>2019-03-SC-C430:2</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5782,12 +5491,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
-      <c r="L97" s="2" t="n">
-        <v>143</v>
-      </c>
-      <c r="M97" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -5804,12 +5510,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A530</t>
+          <t>2019-03-SC-A530:1</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5837,12 +5543,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="2" t="n">
-        <v>145</v>
-      </c>
-      <c r="M98" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -5859,12 +5562,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A530</t>
+          <t>2019-03-SC-A530:2</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5892,12 +5595,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K99" s="2" t="inlineStr"/>
-      <c r="L99" s="2" t="n">
-        <v>146</v>
-      </c>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -5914,12 +5614,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B530</t>
+          <t>2019-03-SC-B530:1</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5947,12 +5647,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="2" t="n">
-        <v>148</v>
-      </c>
-      <c r="M100" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -5969,12 +5666,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B530</t>
+          <t>2019-03-SC-B530:2</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -6002,12 +5699,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K101" s="2" t="inlineStr"/>
-      <c r="L101" s="2" t="n">
-        <v>149</v>
-      </c>
-      <c r="M101" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -6024,12 +5718,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C530</t>
+          <t>2019-03-SC-C530:1</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -6057,12 +5751,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K102" s="2" t="inlineStr"/>
-      <c r="L102" s="2" t="n">
-        <v>151</v>
-      </c>
-      <c r="M102" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -6079,12 +5770,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C530</t>
+          <t>2019-03-SC-C530:2</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -6112,12 +5803,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K103" s="2" t="inlineStr"/>
-      <c r="L103" s="2" t="n">
-        <v>152</v>
-      </c>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -6134,12 +5822,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A630</t>
+          <t>2019-03-SC-A630:1</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -6167,12 +5855,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K104" s="2" t="inlineStr"/>
-      <c r="L104" s="2" t="n">
-        <v>154</v>
-      </c>
-      <c r="M104" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -6189,12 +5874,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-A630</t>
+          <t>2019-03-SC-A630:2</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -6222,12 +5907,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K105" s="2" t="inlineStr"/>
-      <c r="L105" s="2" t="n">
-        <v>155</v>
-      </c>
-      <c r="M105" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -6244,12 +5926,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B630</t>
+          <t>2019-03-SC-B630:1</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -6277,12 +5959,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K106" s="2" t="inlineStr"/>
-      <c r="L106" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="M106" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -6299,12 +5978,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-B630</t>
+          <t>2019-03-SC-B630:2</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -6332,12 +6011,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K107" s="2" t="inlineStr"/>
-      <c r="L107" s="2" t="n">
-        <v>158</v>
-      </c>
-      <c r="M107" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -6354,12 +6030,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C630</t>
+          <t>2019-03-SC-C630:1</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -6387,12 +6063,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K108" s="2" t="inlineStr"/>
-      <c r="L108" s="2" t="n">
-        <v>160</v>
-      </c>
-      <c r="M108" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
@@ -6409,12 +6082,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>2019-03-SC-C630</t>
+          <t>2019-03-SC-C630:2</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Sample_ID:Lab_replicate</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -6442,12 +6115,9 @@
         <v>-77.2208</v>
       </c>
       <c r="K109" s="2" t="inlineStr"/>
-      <c r="L109" s="2" t="n">
-        <v>161</v>
-      </c>
-      <c r="M109" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; id not unique: 108 rows share an id; method from the package description</t>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.25581/ornlsfa.024/1837084 package spatialCoverage point; source column Percent_N (percent, unit from data dictionary); depth from Soil_depth_upper, Soil_depth_lower; method from the package description</t>
         </is>
       </c>
     </row>
